--- a/report/spending_by_weekday.xlsx
+++ b/report/spending_by_weekday.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,111 +433,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Понедельник</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3335.45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Вторник</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>443.55</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Среда</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1534.33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Четверг</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>871.74</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1118.16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Суббота</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>356.56</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Воскресенье</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>351.7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
